--- a/docs/PostgreSQL移行・改修まとめ.xlsx
+++ b/docs/PostgreSQL移行・改修まとめ.xlsx
@@ -1,13 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54A8FE3-5025-4A27-BF1E-39C1FA90EE12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="概要" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="PostgreSQLセットアップ手順" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="改修内容一覧" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="動作確認手順" state="visible" r:id="rId7"/>
+    <sheet name="概要" sheetId="1" r:id="rId1"/>
+    <sheet name="PostgreSQLセットアップ手順" sheetId="2" r:id="rId2"/>
+    <sheet name="改修内容一覧" sheetId="3" r:id="rId3"/>
+    <sheet name="動作確認手順" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -106,9 +110,6 @@
     <t>方法B：公式インストーラ</t>
   </si>
   <si>
-    <t>https://www.postgresql.org/download/windows/ からインストーラをダウンロードして実行</t>
-  </si>
-  <si>
     <t>インストール時の注意</t>
   </si>
   <si>
@@ -121,7 +122,7 @@
     <t>インストール後、「SQL Shell (psql)」を起動（もしくは psql -U postgres）し、以下を実行する</t>
   </si>
   <si>
-    <t xml:space="preserve">CREATE DATABASE beautypos;
+    <t>CREATE DATABASE beautypos;
 CREATE USER beautypos_user WITH PASSWORD 'beautypos_pass';
 GRANT ALL PRIVILEGES ON DATABASE beautypos TO beautypos_user;</t>
   </si>
@@ -132,7 +133,7 @@
     <t>beautyPOSの application.properties は、上記②のデフォルト値（beautypos / beautypos_user / beautypos_pass）を前提にしているため、②のとおり作成すれば追加設定は不要。値を変えたい場合のみ、起動前に環境変数を設定する（PowerShellの例）</t>
   </si>
   <si>
-    <t xml:space="preserve">$env:DB_URL = "jdbc:postgresql://localhost:5432/beautypos"
+    <t>$env:DB_URL = "jdbc:postgresql://localhost:5432/beautypos"
 $env:DB_USERNAME = "beautypos_user"
 $env:DB_PASSWORD = "beautypos_pass"</t>
   </si>
@@ -342,58 +343,89 @@
   </si>
   <si>
     <t>初回コミットが記録されている</t>
+  </si>
+  <si>
+    <t>https://www.postgresql.org/download/windows/ からインストーラをダウンロードして実行</t>
+    <phoneticPr fontId="8"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="20"/>
       <color rgb="FFD17A9C"/>
-      <sz val="20"/>
       <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF8A7377"/>
-      <sz val="11"/>
       <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <b/>
+      <sz val="13"/>
       <color rgb="FFD17A9C"/>
-      <sz val="13"/>
       <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <b/>
+      <sz val="10.5"/>
       <color rgb="FF4A3B3F"/>
-      <sz val="10.5"/>
       <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
+      <sz val="10.5"/>
       <color rgb="FF4A3B3F"/>
-      <sz val="10.5"/>
       <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
+      <sz val="9.5"/>
       <color rgb="FFE6DCC8"/>
-      <sz val="9.5"/>
       <name val="Consolas"/>
     </font>
     <font>
       <b/>
+      <sz val="10.5"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="10.5"/>
       <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -482,11 +514,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -502,31 +550,22 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -862,491 +901,498 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FFD17A9C"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:I18"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="34" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:9" ht="34" customHeight="1">
+      <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" spans="2:9" ht="18" customHeight="1">
+      <c r="B3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+    </row>
+    <row r="5" spans="2:9" ht="22" customHeight="1">
+      <c r="B5" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-    </row>
-    <row r="6" ht="34" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+    </row>
+    <row r="6" spans="2:9" ht="34" customHeight="1">
+      <c r="B6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="5" t="s">
+      <c r="C6" s="9"/>
+      <c r="D6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-    </row>
-    <row r="7" ht="34" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+    </row>
+    <row r="7" spans="2:9" ht="34" customHeight="1">
+      <c r="B7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5" t="s">
+      <c r="C7" s="9"/>
+      <c r="D7" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-    </row>
-    <row r="8" ht="34" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+    </row>
+    <row r="8" spans="2:9" ht="34" customHeight="1">
+      <c r="B8" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="5" t="s">
+      <c r="C8" s="9"/>
+      <c r="D8" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-    </row>
-    <row r="9" ht="20" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+    </row>
+    <row r="9" spans="2:9" ht="20" customHeight="1">
+      <c r="B9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="5" t="s">
+      <c r="C9" s="9"/>
+      <c r="D9" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-    </row>
-    <row r="10" ht="34" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+    </row>
+    <row r="10" spans="2:9" ht="34" customHeight="1">
+      <c r="B10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="5" t="s">
+      <c r="C10" s="9"/>
+      <c r="D10" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+    </row>
+    <row r="13" spans="2:9" ht="22" customHeight="1">
+      <c r="B13" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-    </row>
-    <row r="14" ht="20" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" spans="2:9" ht="20" customHeight="1">
+      <c r="B14" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="5" t="s">
+      <c r="C14" s="9"/>
+      <c r="D14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-    </row>
-    <row r="15" ht="20" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="4" t="s">
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+    </row>
+    <row r="15" spans="2:9" ht="20" customHeight="1">
+      <c r="B15" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="5" t="s">
+      <c r="C15" s="9"/>
+      <c r="D15" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-    </row>
-    <row r="16" ht="20" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="4" t="s">
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+    </row>
+    <row r="16" spans="2:9" ht="20" customHeight="1">
+      <c r="B16" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="5" t="s">
+      <c r="C16" s="9"/>
+      <c r="D16" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-    </row>
-    <row r="17" ht="20" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="4" t="s">
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+    </row>
+    <row r="17" spans="2:9" ht="20" customHeight="1">
+      <c r="B17" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="5" t="s">
+      <c r="C17" s="9"/>
+      <c r="D17" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-    </row>
-    <row r="18" ht="20" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+    </row>
+    <row r="18" spans="2:9" ht="20" customHeight="1">
+      <c r="B18" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="5" t="s">
+      <c r="C18" s="9"/>
+      <c r="D18" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:I6"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:I15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:I16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:I17"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:I14"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:I7"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="D8:I8"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D9:I9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="B13:I13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:I15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:I16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:I17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:I6"/>
   </mergeCells>
-  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FFC9A961"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:I24"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="34" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:9" ht="34" customHeight="1">
+      <c r="B2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" spans="2:9" ht="18" customHeight="1">
+      <c r="B3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+    </row>
+    <row r="5" spans="2:9" ht="22" customHeight="1">
+      <c r="B5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-    </row>
-    <row r="6" ht="34" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+    </row>
+    <row r="6" spans="2:9" ht="34" customHeight="1">
+      <c r="B6" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="5" t="s">
+      <c r="C6" s="9"/>
+      <c r="D6" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-    </row>
-    <row r="7" ht="34" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+    </row>
+    <row r="7" spans="2:9" ht="34" customHeight="1">
+      <c r="B7" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5" t="s">
+      <c r="C7" s="9"/>
+      <c r="D7" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+    </row>
+    <row r="8" spans="2:9" ht="34" customHeight="1">
+      <c r="B8" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-    </row>
-    <row r="8" ht="34" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="9"/>
+      <c r="D8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+    </row>
+    <row r="11" spans="2:9" ht="22" customHeight="1">
+      <c r="B11" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+    </row>
+    <row r="12" spans="2:9" ht="51" customHeight="1">
+      <c r="B12" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-    </row>
-    <row r="12" ht="20" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+    </row>
+    <row r="13" spans="2:9" ht="90" customHeight="1">
+      <c r="B13" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-    </row>
-    <row r="13" ht="90" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="7" t="s">
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+    </row>
+    <row r="16" spans="2:9" ht="22" customHeight="1">
+      <c r="B16" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-    </row>
-    <row r="16" ht="22" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+    </row>
+    <row r="17" spans="2:9" ht="65.5" customHeight="1">
+      <c r="B17" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-    </row>
-    <row r="17" ht="46" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="8" t="s">
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+    </row>
+    <row r="18" spans="2:9" ht="80" customHeight="1">
+      <c r="B18" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-    </row>
-    <row r="18" ht="80" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="7" t="s">
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+    </row>
+    <row r="21" spans="2:9" ht="22" customHeight="1">
+      <c r="B21" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-    </row>
-    <row r="21" ht="22" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+    </row>
+    <row r="22" spans="2:9" ht="20" customHeight="1">
+      <c r="B22" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-    </row>
-    <row r="22" ht="20" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B22" s="4" t="s">
+      <c r="C22" s="9"/>
+      <c r="D22" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="5" t="s">
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+    </row>
+    <row r="23" spans="2:9" ht="33.5" customHeight="1">
+      <c r="B23" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-    </row>
-    <row r="23" ht="20" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B23" s="4" t="s">
+      <c r="C23" s="9"/>
+      <c r="D23" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="5" t="s">
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+    </row>
+    <row r="24" spans="2:9" ht="43" customHeight="1">
+      <c r="B24" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-    </row>
-    <row r="24" ht="20" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B24" s="4" t="s">
+      <c r="C24" s="9"/>
+      <c r="D24" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:I24"/>
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:I22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:I23"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="B18:I18"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:I7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="B11:I11"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="B5:I5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D6:I6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:I7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B13:I13"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="B18:I18"/>
-    <mergeCell ref="B21:I21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:I22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:I23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:I24"/>
   </mergeCells>
-  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <phoneticPr fontId="8"/>
+  <hyperlinks>
+    <hyperlink ref="D7" r:id="rId1" xr:uid="{A9F5B8D2-B045-43A6-AF46-27272601B030}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FFD17A9C"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:H14"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="4" customWidth="1"/>
@@ -1355,213 +1401,213 @@
     <col min="5" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="34" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:8" ht="34" customHeight="1">
+      <c r="B2" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+    </row>
+    <row r="3" spans="2:8" ht="18" customHeight="1">
+      <c r="B3" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+    </row>
+    <row r="4" spans="2:8" ht="22" customHeight="1">
+      <c r="B4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
+      <c r="C4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="D4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="E4" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="9" t="s">
+    </row>
+    <row r="5" spans="2:8" ht="46" customHeight="1">
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="5" ht="46" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="10">
-        <v>1</v>
-      </c>
-      <c r="C5" s="10" t="s">
+      <c r="D5" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="F5" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="11" t="s">
+    </row>
+    <row r="6" spans="2:8" ht="46" customHeight="1">
+      <c r="B6" s="4">
+        <v>2</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="6" ht="46" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="12">
-        <v>2</v>
-      </c>
-      <c r="C6" s="12" t="s">
+      <c r="D6" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="E6" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="F6" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="13" t="s">
+    </row>
+    <row r="7" spans="2:8" ht="46" customHeight="1">
+      <c r="B7" s="2">
+        <v>3</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" ht="46" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="10">
-        <v>3</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="11" t="s">
+      <c r="E7" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="F7" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F7" s="11" t="s">
+    </row>
+    <row r="8" spans="2:8" ht="46" customHeight="1">
+      <c r="B8" s="4">
+        <v>4</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="8" ht="46" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="12">
-        <v>4</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8" s="13" t="s">
+      <c r="E8" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="F8" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="13" t="s">
+    </row>
+    <row r="9" spans="2:8" ht="46" customHeight="1">
+      <c r="B9" s="2">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="9" ht="46" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="10">
-        <v>5</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="11" t="s">
+      <c r="E9" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="F9" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F9" s="11" t="s">
+    </row>
+    <row r="10" spans="2:8" ht="46" customHeight="1">
+      <c r="B10" s="4">
+        <v>6</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="10" ht="46" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="12">
-        <v>6</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" s="13" t="s">
+      <c r="E10" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="F10" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F10" s="13" t="s">
+    </row>
+    <row r="11" spans="2:8" ht="46" customHeight="1">
+      <c r="B11" s="2">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="11" ht="46" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="10">
-        <v>7</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="11" t="s">
+      <c r="E11" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="F11" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F11" s="11" t="s">
+    </row>
+    <row r="12" spans="2:8" ht="46" customHeight="1">
+      <c r="B12" s="4">
+        <v>8</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="12" ht="46" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="12">
-        <v>8</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" s="13" t="s">
+      <c r="E12" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="F12" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F12" s="13" t="s">
+    </row>
+    <row r="13" spans="2:8" ht="46" customHeight="1">
+      <c r="B13" s="2">
+        <v>9</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="13" ht="46" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="10">
-        <v>9</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="11" t="s">
+      <c r="E13" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="F13" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F13" s="11" t="s">
+    </row>
+    <row r="14" spans="2:8" ht="46" customHeight="1">
+      <c r="B14" s="4">
+        <v>10</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="14" ht="46" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="12">
-        <v>10</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="13" t="s">
+      <c r="E14" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="F14" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1569,18 +1615,20 @@
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
   </mergeCells>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup fitToHeight="0" orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FFC9A961"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:F10"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="4" customWidth="1"/>
@@ -1588,120 +1636,120 @@
     <col min="4" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="34" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:6" ht="34" customHeight="1">
+      <c r="B2" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+    </row>
+    <row r="3" spans="2:6" ht="18" customHeight="1">
+      <c r="B3" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="2:6" ht="22" customHeight="1">
+      <c r="B4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="9" t="s">
+      <c r="D4" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="E4" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="9" t="s">
+    </row>
+    <row r="5" spans="2:6" ht="44" customHeight="1">
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="5" ht="44" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="10">
-        <v>1</v>
-      </c>
-      <c r="C5" s="11" t="s">
+      <c r="D5" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="11" t="s">
+    </row>
+    <row r="6" spans="2:6" ht="44" customHeight="1">
+      <c r="B6" s="4">
+        <v>2</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="6" ht="44" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="12">
-        <v>2</v>
-      </c>
-      <c r="C6" s="13" t="s">
+      <c r="D6" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="E6" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="E6" s="13" t="s">
+    </row>
+    <row r="7" spans="2:6" ht="44" customHeight="1">
+      <c r="B7" s="2">
+        <v>3</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="7" ht="44" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="10">
-        <v>3</v>
-      </c>
-      <c r="C7" s="11" t="s">
+      <c r="D7" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="E7" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E7" s="11" t="s">
+    </row>
+    <row r="8" spans="2:6" ht="44" customHeight="1">
+      <c r="B8" s="4">
+        <v>4</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="8" ht="44" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="12">
-        <v>4</v>
-      </c>
-      <c r="C8" s="13" t="s">
+      <c r="D8" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="E8" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E8" s="13" t="s">
+    </row>
+    <row r="9" spans="2:6" ht="44" customHeight="1">
+      <c r="B9" s="2">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="9" ht="44" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="10">
-        <v>5</v>
-      </c>
-      <c r="C9" s="11" t="s">
+      <c r="D9" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="E9" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E9" s="11" t="s">
+    </row>
+    <row r="10" spans="2:6" ht="44" customHeight="1">
+      <c r="B10" s="4">
+        <v>6</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="10" ht="44" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="12">
-        <v>6</v>
-      </c>
-      <c r="C10" s="13" t="s">
+      <c r="D10" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="E10" s="5" t="s">
         <v>106</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1709,6 +1757,8 @@
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B3:F3"/>
   </mergeCells>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup fitToHeight="0" orientation="landscape"/>
 </worksheet>
 </file>